--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R90945c8af4644502"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R121e3338204348f2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R121e3338204348f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbaee392e98c34249"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbaee392e98c34249"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Refb8fecae0fb45d2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Refb8fecae0fb45d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rab0bb9a6fadc4d0e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rab0bb9a6fadc4d0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2daa406ae2e34b57"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2daa406ae2e34b57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96d623742ac643f3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96d623742ac643f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfb3109941e9f4b00"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfb3109941e9f4b00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89481c6d3e32412a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89481c6d3e32412a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R936a11c521024272"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R936a11c521024272"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6caec52fe37b4130"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6caec52fe37b4130"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0aa38ef49e9744bc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0aa38ef49e9744bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R55957d585ad74715"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R55957d585ad74715"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R75c51ffe59ff49c6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R75c51ffe59ff49c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R75b36a912e494ea9"/>
   </x:sheets>
 </x:workbook>
 </file>
